--- a/db/data/कर्मचारी विवरण.xlsx
+++ b/db/data/कर्मचारी विवरण.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="22624"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dell\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pradeep\Desktop\storemgmt\db\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E903F078-2CE8-4B87-A0C4-77128D55B800}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755" activeTab="3"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
-    <sheet name="076-06-08" sheetId="4" r:id="rId4"/>
+    <sheet name="076-06-08" sheetId="4" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'076-06-08'!$A$1:$P$27</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$F$36</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">Sheet2!$A$1:$E$36</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">Sheet2!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Sheet1!$A$1:$F$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">Sheet2!$A$1:$E$36</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">Sheet2!$1:$4</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="165">
   <si>
     <t>शेषकान्त पाण्डे</t>
   </si>
@@ -380,116 +380,167 @@
     <t>महिला कार्यकर्ता</t>
   </si>
   <si>
-    <t>कर्मचारी संकेत नं</t>
-  </si>
-  <si>
-    <t>कर्मचारीको स्थायी ठेगाना</t>
-  </si>
-  <si>
-    <t>सेवा/समुह</t>
-  </si>
-  <si>
-    <t>हालको पदमा नियुक्ति मिति</t>
-  </si>
-  <si>
-    <t xml:space="preserve">समायोजन भएको </t>
-  </si>
-  <si>
-    <t>मोबाइल नं</t>
-  </si>
-  <si>
-    <t>संघ</t>
-  </si>
-  <si>
-    <t>प्रदेश</t>
-  </si>
-  <si>
-    <t>स्थानीय</t>
-  </si>
-  <si>
-    <t>पद पूर्तिको अवस्था</t>
-  </si>
-  <si>
-    <t>रिक्त</t>
-  </si>
-  <si>
-    <t>पूर्ति</t>
-  </si>
-  <si>
-    <t>हाजिर हुन नआएको</t>
-  </si>
-  <si>
-    <t>नेपाल सरकार</t>
-  </si>
-  <si>
-    <t>सङ्घीय मामिला तथा सामान्य प्रशासन मन्त्रालय</t>
-  </si>
-  <si>
-    <t>कर्मचारी विवरण संकलन फाराम</t>
-  </si>
-  <si>
-    <t>कार्यालयको नाम: खानेपानी तथा सरसफाई कार्यालय</t>
-  </si>
-  <si>
-    <t>कार्यालयको ठेगाना: गण्डकी प्रदेश, तनहुँ</t>
-  </si>
-  <si>
-    <t>करार</t>
-  </si>
-  <si>
-    <t>ने.ई/सिभिल/स्या.</t>
-  </si>
-  <si>
-    <t>ने.प्र/सा.प्र</t>
-  </si>
-  <si>
-    <t>ने.प्र./लेखा</t>
-  </si>
-  <si>
-    <t>ने.वि.</t>
-  </si>
-  <si>
-    <t>ने. वि.</t>
-  </si>
-  <si>
-    <t>ने.प्र./सा.प्र.</t>
-  </si>
-  <si>
-    <t>√</t>
-  </si>
-  <si>
-    <t>डिभिजन प्रमुख (नवौं)</t>
-  </si>
-  <si>
-    <t>इन्जिनियर आठौँ</t>
-  </si>
-  <si>
-    <t>लेखा अधिकृत छैठौं</t>
-  </si>
-  <si>
-    <t>कम्प्युटर अधिकृत छैठौँ</t>
-  </si>
-  <si>
-    <t>सब इन्जिनियर पाँचौं)</t>
-  </si>
-  <si>
-    <t>सब इन्जिनियर (पाँचौं)</t>
-  </si>
-  <si>
-    <t>महिला कार्यकर्ता (पाँचौं)</t>
-  </si>
-  <si>
-    <t>खा. पा. स. टे. (पाँचौं)</t>
+    <t>ctroll</t>
+  </si>
+  <si>
+    <t>name_ne</t>
+  </si>
+  <si>
+    <t>name_en</t>
+  </si>
+  <si>
+    <t>Hari Prasad Timilsina</t>
+  </si>
+  <si>
+    <t>Indra Pratap Bohara</t>
+  </si>
+  <si>
+    <t>Prem Bahadur Thapa</t>
+  </si>
+  <si>
+    <t>Ramchandra Pandit</t>
+  </si>
+  <si>
+    <t>Gyan Narayan shreshtha</t>
+  </si>
+  <si>
+    <t>Pradeep Sapkota</t>
+  </si>
+  <si>
+    <t>Dilliram Bastola</t>
+  </si>
+  <si>
+    <t>Kedar Pantha</t>
+  </si>
+  <si>
+    <t>Binu Lohani</t>
+  </si>
+  <si>
+    <t>Mina Kumari Shreshtha</t>
+  </si>
+  <si>
+    <t>Khem Bahadur Sunuwar</t>
+  </si>
+  <si>
+    <t>Ishwar Ranjitkar</t>
+  </si>
+  <si>
+    <t>Tek Bahadur Pulami</t>
+  </si>
+  <si>
+    <t>Surya Chandra Acharya</t>
+  </si>
+  <si>
+    <t>Tek Bahadur Thapa</t>
+  </si>
+  <si>
+    <t>Padam Bahadur Thapa</t>
+  </si>
+  <si>
+    <t>Bishnu Prasad Giri</t>
+  </si>
+  <si>
+    <t>Jeet Bahadur Bote</t>
+  </si>
+  <si>
+    <t>post</t>
+  </si>
+  <si>
+    <t>service</t>
+  </si>
+  <si>
+    <t>group</t>
+  </si>
+  <si>
+    <t>phone</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>सिभिल</t>
+  </si>
+  <si>
+    <t>सामान्य प्रशासन</t>
+  </si>
+  <si>
+    <t>मेकानिकल</t>
+  </si>
+  <si>
+    <t>नेपाल प्रशासन</t>
+  </si>
+  <si>
+    <t>नेपाल इन्जिनियरिङ</t>
+  </si>
+  <si>
+    <t>नेपाल विविध</t>
+  </si>
+  <si>
+    <t>स्यानिटरी</t>
+  </si>
+  <si>
+    <t>लेखा</t>
+  </si>
+  <si>
+    <t>प्रशासन</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>level_class</t>
+  </si>
+  <si>
+    <t>sub_group</t>
+  </si>
+  <si>
+    <t>working</t>
+  </si>
+  <si>
+    <t>कार्यालय प्रमुख</t>
+  </si>
+  <si>
+    <t>अधिकृत</t>
+  </si>
+  <si>
+    <t>लेखा अधिकृत</t>
+  </si>
+  <si>
+    <t>हलुका सवारी चालक</t>
+  </si>
+  <si>
+    <t>कार्यालय सहयोगी</t>
+  </si>
+  <si>
+    <t>खानेपानी तथा सरसफाई टेक्निसियन</t>
+  </si>
+  <si>
+    <t>अधिकृत आठौँ</t>
+  </si>
+  <si>
+    <t>अधिकृतस्तर आठौँ</t>
+  </si>
+  <si>
+    <t>अधिकृतस्तर नवौं</t>
+  </si>
+  <si>
+    <t>अधिकृतस्तर छैटौं</t>
+  </si>
+  <si>
+    <t>सहायक पाँचौं</t>
+  </si>
+  <si>
+    <t>श्रेणी बिहिन</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-4000439]0"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -557,13 +608,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <color theme="1"/>
-      <name val="Kalimati"/>
-      <charset val="1"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -573,7 +617,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -605,74 +649,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -747,9 +728,7 @@
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -758,69 +737,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -915,6 +831,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -950,6 +883,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1125,9 +1075,665 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A2:L20"/>
+  <sheetFormatPr defaultColWidth="15.7109375" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="2.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="7" customWidth="1"/>
+    <col min="3" max="4" width="17.7109375" style="7" customWidth="1"/>
+    <col min="5" max="6" width="19.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" style="4"/>
+    <col min="11" max="11" width="24.5703125" style="7" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:12" s="26" customFormat="1">
+      <c r="A2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2" t="s">
+        <v>135</v>
+      </c>
+      <c r="G2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H2" t="s">
+        <v>137</v>
+      </c>
+      <c r="I2" t="s">
+        <v>151</v>
+      </c>
+      <c r="J2" t="s">
+        <v>138</v>
+      </c>
+      <c r="K2" t="s">
+        <v>139</v>
+      </c>
+      <c r="L2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="B3">
+        <v>123613</v>
+      </c>
+      <c r="C3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E3" t="s">
+        <v>161</v>
+      </c>
+      <c r="F3" t="s">
+        <v>153</v>
+      </c>
+      <c r="G3" t="s">
+        <v>144</v>
+      </c>
+      <c r="H3" t="s">
+        <v>140</v>
+      </c>
+      <c r="I3" t="s">
+        <v>146</v>
+      </c>
+      <c r="J3">
+        <v>9856060810</v>
+      </c>
+      <c r="K3" t="s">
+        <v>45</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="B4">
+        <v>122954</v>
+      </c>
+      <c r="C4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D4" t="s">
+        <v>118</v>
+      </c>
+      <c r="E4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" t="s">
+        <v>144</v>
+      </c>
+      <c r="H4" t="s">
+        <v>140</v>
+      </c>
+      <c r="I4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J4">
+        <v>9846071948</v>
+      </c>
+      <c r="K4"/>
+      <c r="L4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="B5">
+        <v>135333</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E5" t="s">
+        <v>159</v>
+      </c>
+      <c r="F5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" t="s">
+        <v>144</v>
+      </c>
+      <c r="H5" t="s">
+        <v>140</v>
+      </c>
+      <c r="I5" t="s">
+        <v>146</v>
+      </c>
+      <c r="J5">
+        <v>9856045470</v>
+      </c>
+      <c r="K5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="B6">
+        <v>103982</v>
+      </c>
+      <c r="C6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" t="s">
+        <v>120</v>
+      </c>
+      <c r="E6" t="s">
+        <v>162</v>
+      </c>
+      <c r="F6" t="s">
+        <v>154</v>
+      </c>
+      <c r="G6" t="s">
+        <v>143</v>
+      </c>
+      <c r="H6" t="s">
+        <v>141</v>
+      </c>
+      <c r="I6" t="s">
+        <v>148</v>
+      </c>
+      <c r="J6">
+        <v>985606347</v>
+      </c>
+      <c r="K6" t="s">
+        <v>57</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="B7">
+        <v>190822</v>
+      </c>
+      <c r="C7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" t="s">
+        <v>121</v>
+      </c>
+      <c r="E7" t="s">
+        <v>162</v>
+      </c>
+      <c r="F7" t="s">
+        <v>155</v>
+      </c>
+      <c r="G7" t="s">
+        <v>143</v>
+      </c>
+      <c r="H7" t="s">
+        <v>141</v>
+      </c>
+      <c r="I7" t="s">
+        <v>147</v>
+      </c>
+      <c r="J7">
+        <v>9846111816</v>
+      </c>
+      <c r="K7" t="s">
+        <v>54</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="B8">
+        <v>203926</v>
+      </c>
+      <c r="C8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" t="s">
+        <v>122</v>
+      </c>
+      <c r="E8" t="s">
+        <v>162</v>
+      </c>
+      <c r="F8" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" t="s">
+        <v>145</v>
+      </c>
+      <c r="H8"/>
+      <c r="I8"/>
+      <c r="J8">
+        <v>9857659107</v>
+      </c>
+      <c r="K8" t="s">
+        <v>53</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="B9">
+        <v>150069</v>
+      </c>
+      <c r="C9" t="s">
+        <v>111</v>
+      </c>
+      <c r="D9" t="s">
+        <v>123</v>
+      </c>
+      <c r="E9" t="s">
+        <v>162</v>
+      </c>
+      <c r="F9" t="s">
+        <v>154</v>
+      </c>
+      <c r="G9" t="s">
+        <v>144</v>
+      </c>
+      <c r="H9" t="s">
+        <v>140</v>
+      </c>
+      <c r="I9" t="s">
+        <v>146</v>
+      </c>
+      <c r="J9">
+        <v>9856036830</v>
+      </c>
+      <c r="K9"/>
+      <c r="L9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="B10">
+        <v>129444</v>
+      </c>
+      <c r="C10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E10" t="s">
+        <v>163</v>
+      </c>
+      <c r="F10" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" t="s">
+        <v>144</v>
+      </c>
+      <c r="H10" t="s">
+        <v>140</v>
+      </c>
+      <c r="I10" t="s">
+        <v>146</v>
+      </c>
+      <c r="J10">
+        <v>9846062103</v>
+      </c>
+      <c r="K10"/>
+      <c r="L10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="B11">
+        <v>227510</v>
+      </c>
+      <c r="C11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" t="s">
+        <v>125</v>
+      </c>
+      <c r="E11" t="s">
+        <v>163</v>
+      </c>
+      <c r="F11" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11" t="s">
+        <v>144</v>
+      </c>
+      <c r="H11" t="s">
+        <v>140</v>
+      </c>
+      <c r="I11" t="s">
+        <v>146</v>
+      </c>
+      <c r="J11">
+        <v>9846417379</v>
+      </c>
+      <c r="K11" t="s">
+        <v>46</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="B12">
+        <v>167986</v>
+      </c>
+      <c r="C12" t="s">
+        <v>112</v>
+      </c>
+      <c r="D12" t="s">
+        <v>126</v>
+      </c>
+      <c r="E12" t="s">
+        <v>163</v>
+      </c>
+      <c r="F12" t="s">
+        <v>113</v>
+      </c>
+      <c r="G12" t="s">
+        <v>145</v>
+      </c>
+      <c r="H12"/>
+      <c r="I12"/>
+      <c r="J12">
+        <v>9856080588</v>
+      </c>
+      <c r="K12"/>
+      <c r="L12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="B13">
+        <v>140508</v>
+      </c>
+      <c r="C13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" t="s">
+        <v>127</v>
+      </c>
+      <c r="E13" t="s">
+        <v>163</v>
+      </c>
+      <c r="F13" t="s">
+        <v>158</v>
+      </c>
+      <c r="G13" t="s">
+        <v>144</v>
+      </c>
+      <c r="H13" t="s">
+        <v>140</v>
+      </c>
+      <c r="I13" t="s">
+        <v>146</v>
+      </c>
+      <c r="J13">
+        <v>9846060963</v>
+      </c>
+      <c r="K13" t="s">
+        <v>47</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="B14">
+        <v>166978</v>
+      </c>
+      <c r="C14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" t="s">
+        <v>128</v>
+      </c>
+      <c r="E14" t="s">
+        <v>163</v>
+      </c>
+      <c r="F14" t="s">
+        <v>158</v>
+      </c>
+      <c r="G14" t="s">
+        <v>144</v>
+      </c>
+      <c r="H14" t="s">
+        <v>140</v>
+      </c>
+      <c r="I14" t="s">
+        <v>146</v>
+      </c>
+      <c r="J14">
+        <v>9846030628</v>
+      </c>
+      <c r="K14"/>
+      <c r="L14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="B15">
+        <v>182980</v>
+      </c>
+      <c r="C15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" t="s">
+        <v>129</v>
+      </c>
+      <c r="E15" t="s">
+        <v>163</v>
+      </c>
+      <c r="F15" t="s">
+        <v>158</v>
+      </c>
+      <c r="G15" t="s">
+        <v>144</v>
+      </c>
+      <c r="H15" t="s">
+        <v>140</v>
+      </c>
+      <c r="I15" t="s">
+        <v>146</v>
+      </c>
+      <c r="J15">
+        <v>9845416400</v>
+      </c>
+      <c r="K15"/>
+      <c r="L15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="B16">
+        <v>170653</v>
+      </c>
+      <c r="C16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" t="s">
+        <v>130</v>
+      </c>
+      <c r="E16" t="s">
+        <v>163</v>
+      </c>
+      <c r="F16" t="s">
+        <v>158</v>
+      </c>
+      <c r="G16" t="s">
+        <v>144</v>
+      </c>
+      <c r="H16" t="s">
+        <v>140</v>
+      </c>
+      <c r="I16" t="s">
+        <v>146</v>
+      </c>
+      <c r="J16">
+        <v>9846329585</v>
+      </c>
+      <c r="K16"/>
+      <c r="L16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12">
+      <c r="B17">
+        <v>150701</v>
+      </c>
+      <c r="C17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" t="s">
+        <v>131</v>
+      </c>
+      <c r="E17" t="s">
+        <v>163</v>
+      </c>
+      <c r="F17" t="s">
+        <v>158</v>
+      </c>
+      <c r="G17" t="s">
+        <v>144</v>
+      </c>
+      <c r="H17" t="s">
+        <v>140</v>
+      </c>
+      <c r="I17" t="s">
+        <v>146</v>
+      </c>
+      <c r="J17">
+        <v>9846055789</v>
+      </c>
+      <c r="K17"/>
+      <c r="L17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12">
+      <c r="B18"/>
+      <c r="C18" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" t="s">
+        <v>132</v>
+      </c>
+      <c r="E18" t="s">
+        <v>164</v>
+      </c>
+      <c r="F18" t="s">
+        <v>156</v>
+      </c>
+      <c r="G18" t="s">
+        <v>144</v>
+      </c>
+      <c r="H18" t="s">
+        <v>142</v>
+      </c>
+      <c r="I18" t="s">
+        <v>146</v>
+      </c>
+      <c r="J18"/>
+      <c r="K18"/>
+      <c r="L18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12">
+      <c r="B19">
+        <v>135482</v>
+      </c>
+      <c r="C19" t="s">
+        <v>41</v>
+      </c>
+      <c r="D19" t="s">
+        <v>133</v>
+      </c>
+      <c r="E19" t="s">
+        <v>164</v>
+      </c>
+      <c r="F19" t="s">
+        <v>157</v>
+      </c>
+      <c r="G19" t="s">
+        <v>143</v>
+      </c>
+      <c r="H19" t="s">
+        <v>141</v>
+      </c>
+      <c r="I19" t="s">
+        <v>148</v>
+      </c>
+      <c r="J19">
+        <v>9846233996</v>
+      </c>
+      <c r="K19"/>
+      <c r="L19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12">
+      <c r="B20">
+        <v>130492</v>
+      </c>
+      <c r="C20" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" t="s">
+        <v>134</v>
+      </c>
+      <c r="E20" t="s">
+        <v>164</v>
+      </c>
+      <c r="F20" t="s">
+        <v>157</v>
+      </c>
+      <c r="G20" t="s">
+        <v>143</v>
+      </c>
+      <c r="H20" t="s">
+        <v>141</v>
+      </c>
+      <c r="I20" t="s">
+        <v>148</v>
+      </c>
+      <c r="J20">
+        <v>9846090694</v>
+      </c>
+      <c r="K20"/>
+      <c r="L20">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
+  <pageMargins left="0.71" right="0.26" top="0.34" bottom="0.26" header="0.3" footer="0.3"/>
+  <pageSetup scale="62" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F40"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" customWidth="1"/>
     <col min="2" max="2" width="17.7109375" style="7" customWidth="1"/>
@@ -1137,7 +1743,7 @@
     <col min="6" max="6" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="21" customHeight="1">
       <c r="A1" s="27" t="s">
         <v>32</v>
       </c>
@@ -1147,7 +1753,7 @@
       <c r="E1" s="27"/>
       <c r="F1" s="27"/>
     </row>
-    <row r="2" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="21" customHeight="1">
       <c r="A2" s="27" t="s">
         <v>44</v>
       </c>
@@ -1157,7 +1763,7 @@
       <c r="E2" s="27"/>
       <c r="F2" s="27"/>
     </row>
-    <row r="3" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="21" customHeight="1">
       <c r="A3" s="5" t="s">
         <v>33</v>
       </c>
@@ -1177,7 +1783,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="21" customHeight="1">
       <c r="A4" s="15">
         <v>1</v>
       </c>
@@ -1197,7 +1803,7 @@
         <v>9841600280</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="21" customHeight="1">
       <c r="A5" s="15">
         <v>2</v>
       </c>
@@ -1213,7 +1819,7 @@
       <c r="E5" s="12"/>
       <c r="F5" s="9"/>
     </row>
-    <row r="6" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="21" customHeight="1">
       <c r="A6" s="15">
         <v>3</v>
       </c>
@@ -1229,7 +1835,7 @@
       <c r="E6" s="12"/>
       <c r="F6" s="9"/>
     </row>
-    <row r="7" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="21" customHeight="1">
       <c r="A7" s="15">
         <v>4</v>
       </c>
@@ -1247,7 +1853,7 @@
       </c>
       <c r="F7" s="9"/>
     </row>
-    <row r="8" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="21" customHeight="1">
       <c r="A8" s="15">
         <v>5</v>
       </c>
@@ -1265,7 +1871,7 @@
       </c>
       <c r="F8" s="9"/>
     </row>
-    <row r="9" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="21" customHeight="1">
       <c r="A9" s="15">
         <v>6</v>
       </c>
@@ -1283,7 +1889,7 @@
       </c>
       <c r="F9" s="9"/>
     </row>
-    <row r="10" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="21" customHeight="1">
       <c r="A10" s="15">
         <v>7</v>
       </c>
@@ -1303,7 +1909,7 @@
         <v>9856011816</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="21" customHeight="1">
       <c r="A11" s="15">
         <v>8</v>
       </c>
@@ -1321,7 +1927,7 @@
       </c>
       <c r="F11" s="9"/>
     </row>
-    <row r="12" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="21" customHeight="1">
       <c r="A12" s="15">
         <v>9</v>
       </c>
@@ -1337,7 +1943,7 @@
       <c r="E12" s="13"/>
       <c r="F12" s="9"/>
     </row>
-    <row r="13" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="21" customHeight="1">
       <c r="A13" s="15">
         <v>10</v>
       </c>
@@ -1353,7 +1959,7 @@
       <c r="E13" s="13"/>
       <c r="F13" s="9"/>
     </row>
-    <row r="14" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="21" customHeight="1">
       <c r="A14" s="15">
         <v>11</v>
       </c>
@@ -1369,7 +1975,7 @@
       <c r="E14" s="13"/>
       <c r="F14" s="9"/>
     </row>
-    <row r="15" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="21" customHeight="1">
       <c r="A15" s="15">
         <v>12</v>
       </c>
@@ -1385,7 +1991,7 @@
       <c r="E15" s="13"/>
       <c r="F15" s="9"/>
     </row>
-    <row r="16" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="21" customHeight="1">
       <c r="A16" s="15">
         <v>13</v>
       </c>
@@ -1403,7 +2009,7 @@
       </c>
       <c r="F16" s="9"/>
     </row>
-    <row r="17" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="21" customHeight="1">
       <c r="A17" s="15">
         <v>14</v>
       </c>
@@ -1417,7 +2023,7 @@
       <c r="E17" s="13"/>
       <c r="F17" s="9"/>
     </row>
-    <row r="18" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="21" customHeight="1">
       <c r="A18" s="15">
         <v>15</v>
       </c>
@@ -1433,7 +2039,7 @@
       <c r="E18" s="13"/>
       <c r="F18" s="9"/>
     </row>
-    <row r="19" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="21" customHeight="1">
       <c r="A19" s="15">
         <v>16</v>
       </c>
@@ -1451,7 +2057,7 @@
       </c>
       <c r="F19" s="9"/>
     </row>
-    <row r="20" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="21" customHeight="1">
       <c r="A20" s="15">
         <v>17</v>
       </c>
@@ -1467,7 +2073,7 @@
       <c r="E20" s="13"/>
       <c r="F20" s="9"/>
     </row>
-    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="21" customHeight="1">
       <c r="A21" s="15">
         <v>18</v>
       </c>
@@ -1485,7 +2091,7 @@
       </c>
       <c r="F21" s="9"/>
     </row>
-    <row r="22" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="21" customHeight="1">
       <c r="A22" s="15">
         <v>19</v>
       </c>
@@ -1501,7 +2107,7 @@
       <c r="E22" s="12"/>
       <c r="F22" s="9"/>
     </row>
-    <row r="23" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="21" customHeight="1">
       <c r="A23" s="15">
         <v>20</v>
       </c>
@@ -1517,7 +2123,7 @@
       <c r="E23" s="12"/>
       <c r="F23" s="9"/>
     </row>
-    <row r="24" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="21" customHeight="1">
       <c r="A24" s="15">
         <v>21</v>
       </c>
@@ -1533,7 +2139,7 @@
       <c r="E24" s="12"/>
       <c r="F24" s="9"/>
     </row>
-    <row r="25" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="21" customHeight="1">
       <c r="A25" s="15">
         <v>22</v>
       </c>
@@ -1549,7 +2155,7 @@
       <c r="E25" s="6"/>
       <c r="F25" s="9"/>
     </row>
-    <row r="26" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="21" customHeight="1">
       <c r="A26" s="15">
         <v>23</v>
       </c>
@@ -1567,7 +2173,7 @@
       </c>
       <c r="F26" s="9"/>
     </row>
-    <row r="27" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="21" customHeight="1">
       <c r="A27" s="15">
         <v>24</v>
       </c>
@@ -1583,7 +2189,7 @@
       <c r="E27" s="6"/>
       <c r="F27" s="9"/>
     </row>
-    <row r="28" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="21" customHeight="1">
       <c r="A28" s="15">
         <v>25</v>
       </c>
@@ -1599,7 +2205,7 @@
       <c r="E28" s="6"/>
       <c r="F28" s="9"/>
     </row>
-    <row r="29" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="21" customHeight="1">
       <c r="A29" s="15">
         <v>26</v>
       </c>
@@ -1615,7 +2221,7 @@
       <c r="E29" s="6"/>
       <c r="F29" s="9"/>
     </row>
-    <row r="30" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="21" customHeight="1">
       <c r="A30" s="15">
         <v>27</v>
       </c>
@@ -1631,7 +2237,7 @@
       <c r="E30" s="6"/>
       <c r="F30" s="9"/>
     </row>
-    <row r="31" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="21" customHeight="1">
       <c r="A31" s="15">
         <v>28</v>
       </c>
@@ -1647,7 +2253,7 @@
       <c r="E31" s="6"/>
       <c r="F31" s="9"/>
     </row>
-    <row r="32" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="21" customHeight="1">
       <c r="A32" s="15">
         <v>29</v>
       </c>
@@ -1663,7 +2269,7 @@
       <c r="E32" s="6"/>
       <c r="F32" s="9"/>
     </row>
-    <row r="33" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="21" customHeight="1">
       <c r="A33" s="15">
         <v>30</v>
       </c>
@@ -1679,7 +2285,7 @@
       <c r="E33" s="6"/>
       <c r="F33" s="9"/>
     </row>
-    <row r="34" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="21" customHeight="1">
       <c r="A34" s="15">
         <v>31</v>
       </c>
@@ -1695,7 +2301,7 @@
       <c r="E34" s="6"/>
       <c r="F34" s="9"/>
     </row>
-    <row r="35" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="21" customHeight="1">
       <c r="A35" s="15">
         <v>32</v>
       </c>
@@ -1711,7 +2317,7 @@
       <c r="E35" s="6"/>
       <c r="F35" s="9"/>
     </row>
-    <row r="36" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="21" customHeight="1">
       <c r="A36" s="15">
         <v>33</v>
       </c>
@@ -1725,7 +2331,7 @@
       <c r="E36" s="6"/>
       <c r="F36" s="9"/>
     </row>
-    <row r="37" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" ht="21" customHeight="1">
       <c r="A37" s="2">
         <v>31</v>
       </c>
@@ -1735,7 +2341,7 @@
       <c r="E37" s="6"/>
       <c r="F37" s="9"/>
     </row>
-    <row r="38" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="21" customHeight="1">
       <c r="A38" s="2">
         <v>32</v>
       </c>
@@ -1745,7 +2351,7 @@
       <c r="E38" s="6"/>
       <c r="F38" s="9"/>
     </row>
-    <row r="39" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" ht="21" customHeight="1">
       <c r="A39" s="2">
         <v>33</v>
       </c>
@@ -1755,7 +2361,7 @@
       <c r="E39" s="6"/>
       <c r="F39" s="9"/>
     </row>
-    <row r="40" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" ht="21" customHeight="1">
       <c r="A40" s="2">
         <v>34</v>
       </c>
@@ -1775,10 +2381,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E36"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="24" customWidth="1"/>
     <col min="2" max="2" width="33.42578125" style="18" customWidth="1"/>
@@ -1788,7 +2394,7 @@
     <col min="6" max="16384" width="9.140625" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28.5" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:5" ht="18">
       <c r="A1" s="29" t="s">
         <v>80</v>
       </c>
@@ -1797,7 +2403,7 @@
       <c r="D1" s="29"/>
       <c r="E1" s="29"/>
     </row>
-    <row r="2" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="2" spans="1:5" ht="28.5" customHeight="1">
       <c r="A2" s="29" t="s">
         <v>32</v>
       </c>
@@ -1806,7 +2412,7 @@
       <c r="D2" s="29"/>
       <c r="E2" s="29"/>
     </row>
-    <row r="3" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="3" spans="1:5" ht="53.25" customHeight="1">
       <c r="A3" s="28" t="s">
         <v>58</v>
       </c>
@@ -1815,7 +2421,7 @@
       <c r="D3" s="28"/>
       <c r="E3" s="28"/>
     </row>
-    <row r="4" spans="1:5" ht="86.25" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:5" ht="86.25" customHeight="1">
       <c r="A4" s="19" t="s">
         <v>33</v>
       </c>
@@ -1832,7 +2438,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="28.5" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:5" ht="18">
       <c r="A5" s="21">
         <v>1</v>
       </c>
@@ -1849,7 +2455,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="57" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:5" ht="36">
       <c r="A6" s="21">
         <v>2</v>
       </c>
@@ -1866,7 +2472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="28.5" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:5" ht="18">
       <c r="A7" s="21">
         <v>3</v>
       </c>
@@ -1883,7 +2489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="28.5" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:5" ht="18">
       <c r="A8" s="21">
         <v>4</v>
       </c>
@@ -1900,7 +2506,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="28.5" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:5" ht="18">
       <c r="A9" s="21">
         <v>5</v>
       </c>
@@ -1917,7 +2523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="28.5" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:5" ht="18">
       <c r="A10" s="21">
         <v>6</v>
       </c>
@@ -1934,7 +2540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="57" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:5" ht="36">
       <c r="A11" s="21">
         <v>7</v>
       </c>
@@ -1951,7 +2557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="28.5" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:5" ht="18">
       <c r="A12" s="21">
         <v>8</v>
       </c>
@@ -1968,7 +2574,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="28.5" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:5" ht="18">
       <c r="A13" s="21">
         <v>9</v>
       </c>
@@ -1985,7 +2591,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="28.5" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:5" ht="18">
       <c r="A14" s="21">
         <v>10</v>
       </c>
@@ -2002,7 +2608,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="28.5" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:5" ht="18">
       <c r="A15" s="21">
         <v>11</v>
       </c>
@@ -2019,7 +2625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="28.5" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:5" ht="18">
       <c r="A16" s="21">
         <v>12</v>
       </c>
@@ -2036,7 +2642,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="57" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:5" ht="36">
       <c r="A17" s="21">
         <v>13</v>
       </c>
@@ -2053,7 +2659,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="28.5" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:5" ht="18">
       <c r="A18" s="21">
         <v>14</v>
       </c>
@@ -2070,7 +2676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="28.5" x14ac:dyDescent="0.6">
+    <row r="19" spans="1:5" ht="18">
       <c r="A19" s="21">
         <v>15</v>
       </c>
@@ -2087,7 +2693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="57" x14ac:dyDescent="0.6">
+    <row r="20" spans="1:5" ht="18">
       <c r="A20" s="21">
         <v>16</v>
       </c>
@@ -2104,7 +2710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="28.5" x14ac:dyDescent="0.6">
+    <row r="21" spans="1:5" ht="18">
       <c r="A21" s="21">
         <v>17</v>
       </c>
@@ -2121,7 +2727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="57" x14ac:dyDescent="0.6">
+    <row r="22" spans="1:5" ht="36">
       <c r="A22" s="21">
         <v>18</v>
       </c>
@@ -2138,7 +2744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="57" x14ac:dyDescent="0.6">
+    <row r="23" spans="1:5" ht="36">
       <c r="A23" s="21">
         <v>19</v>
       </c>
@@ -2155,7 +2761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="28.5" x14ac:dyDescent="0.6">
+    <row r="24" spans="1:5" ht="18">
       <c r="A24" s="21">
         <v>20</v>
       </c>
@@ -2172,7 +2778,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="28.5" x14ac:dyDescent="0.6">
+    <row r="25" spans="1:5" ht="18">
       <c r="A25" s="21">
         <v>21</v>
       </c>
@@ -2189,7 +2795,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="28.5" x14ac:dyDescent="0.6">
+    <row r="26" spans="1:5" ht="18">
       <c r="A26" s="21">
         <v>22</v>
       </c>
@@ -2206,7 +2812,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="57" x14ac:dyDescent="0.6">
+    <row r="27" spans="1:5" ht="18">
       <c r="A27" s="21">
         <v>23</v>
       </c>
@@ -2223,7 +2829,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="57" x14ac:dyDescent="0.6">
+    <row r="28" spans="1:5" ht="36">
       <c r="A28" s="21">
         <v>24</v>
       </c>
@@ -2240,7 +2846,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="28.5" x14ac:dyDescent="0.6">
+    <row r="29" spans="1:5" ht="18">
       <c r="A29" s="21">
         <v>25</v>
       </c>
@@ -2257,7 +2863,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="57" x14ac:dyDescent="0.6">
+    <row r="30" spans="1:5" ht="18">
       <c r="A30" s="21">
         <v>26</v>
       </c>
@@ -2274,7 +2880,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="46.5" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="31" spans="1:5" ht="46.5" customHeight="1">
       <c r="A31" s="21">
         <v>27</v>
       </c>
@@ -2291,7 +2897,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="32" spans="1:5" ht="39" customHeight="1">
       <c r="A32" s="21">
         <v>28</v>
       </c>
@@ -2308,7 +2914,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="33" spans="1:5" ht="37.5" customHeight="1">
       <c r="A33" s="21">
         <v>29</v>
       </c>
@@ -2325,7 +2931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="34" spans="1:5" ht="42" customHeight="1">
       <c r="A34" s="21">
         <v>30</v>
       </c>
@@ -2342,7 +2948,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="35" spans="1:5" ht="39" customHeight="1">
       <c r="A35" s="21">
         <v>31</v>
       </c>
@@ -2359,7 +2965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="36" spans="1:5" ht="26.25" customHeight="1">
       <c r="A36" s="25"/>
       <c r="B36" s="20"/>
       <c r="C36" s="20" t="s">
@@ -2385,902 +2991,11 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P27"/>
-  <sheetFormatPr defaultColWidth="15.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="6.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="7" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" style="7" customWidth="1"/>
-    <col min="4" max="4" width="17" style="7" customWidth="1"/>
-    <col min="5" max="5" width="19.140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="4.42578125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="4.28515625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="4.42578125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="4"/>
-    <col min="12" max="12" width="24.5703125" style="7" customWidth="1"/>
-    <col min="13" max="13" width="5.42578125" style="7" customWidth="1"/>
-    <col min="14" max="14" width="5.7109375" style="7" customWidth="1"/>
-    <col min="15" max="15" width="7.28515625" style="7" customWidth="1"/>
-    <col min="16" max="16" width="5.42578125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:16" ht="23.25" x14ac:dyDescent="0.6">
-      <c r="A1" s="31" t="s">
-        <v>127</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-    </row>
-    <row r="2" spans="1:16" ht="23.25" x14ac:dyDescent="0.6">
-      <c r="A2" s="30" t="s">
-        <v>128</v>
-      </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="30"/>
-      <c r="O2" s="30"/>
-      <c r="P2" s="30"/>
-    </row>
-    <row r="3" spans="1:16" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="32" t="s">
-        <v>129</v>
-      </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
-      <c r="J3" s="32"/>
-      <c r="K3" s="32"/>
-      <c r="L3" s="32"/>
-      <c r="M3" s="32"/>
-      <c r="N3" s="32"/>
-      <c r="O3" s="32"/>
-      <c r="P3" s="32"/>
-    </row>
-    <row r="4" spans="1:16" ht="24" x14ac:dyDescent="0.25">
-      <c r="A4" s="36" t="s">
-        <v>130</v>
-      </c>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="36"/>
-      <c r="K4" s="36"/>
-      <c r="L4" s="36"/>
-      <c r="M4" s="36"/>
-      <c r="N4" s="36"/>
-      <c r="O4" s="36"/>
-      <c r="P4" s="36"/>
-    </row>
-    <row r="5" spans="1:16" ht="24" x14ac:dyDescent="0.25">
-      <c r="A5" s="37" t="s">
-        <v>131</v>
-      </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="37"/>
-      <c r="I5" s="37"/>
-      <c r="J5" s="37"/>
-      <c r="K5" s="37"/>
-      <c r="L5" s="37"/>
-      <c r="M5" s="37"/>
-      <c r="N5" s="37"/>
-      <c r="O5" s="37"/>
-      <c r="P5" s="37"/>
-    </row>
-    <row r="6" spans="1:16" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="44" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="46" t="s">
-        <v>114</v>
-      </c>
-      <c r="C6" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="40" t="s">
-        <v>115</v>
-      </c>
-      <c r="E6" s="40" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="40" t="s">
-        <v>116</v>
-      </c>
-      <c r="G6" s="49" t="s">
-        <v>117</v>
-      </c>
-      <c r="H6" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="I6" s="34"/>
-      <c r="J6" s="35"/>
-      <c r="K6" s="42" t="s">
-        <v>119</v>
-      </c>
-      <c r="L6" s="40" t="s">
-        <v>43</v>
-      </c>
-      <c r="M6" s="33" t="s">
-        <v>123</v>
-      </c>
-      <c r="N6" s="34"/>
-      <c r="O6" s="35"/>
-      <c r="P6" s="44" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="45"/>
-      <c r="B7" s="47"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="50"/>
-      <c r="H7" s="39" t="s">
-        <v>120</v>
-      </c>
-      <c r="I7" s="39" t="s">
-        <v>121</v>
-      </c>
-      <c r="J7" s="39" t="s">
-        <v>122</v>
-      </c>
-      <c r="K7" s="43"/>
-      <c r="L7" s="41"/>
-      <c r="M7" s="39" t="s">
-        <v>125</v>
-      </c>
-      <c r="N7" s="39" t="s">
-        <v>124</v>
-      </c>
-      <c r="O7" s="48" t="s">
-        <v>126</v>
-      </c>
-      <c r="P7" s="45"/>
-    </row>
-    <row r="8" spans="1:16" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="15">
-        <v>1</v>
-      </c>
-      <c r="B8" s="26">
-        <v>123613</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16" t="s">
-        <v>140</v>
-      </c>
-      <c r="F8" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="J8" s="16"/>
-      <c r="K8" s="11">
-        <v>9856060810</v>
-      </c>
-      <c r="L8" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="M8" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
-      <c r="P8" s="9"/>
-    </row>
-    <row r="9" spans="1:16" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A9" s="15">
-        <v>3</v>
-      </c>
-      <c r="B9" s="26">
-        <v>122954</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16" t="s">
-        <v>141</v>
-      </c>
-      <c r="F9" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="J9" s="16"/>
-      <c r="K9" s="11">
-        <v>9846071948</v>
-      </c>
-      <c r="L9" s="12"/>
-      <c r="M9" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="N9" s="12"/>
-      <c r="O9" s="12"/>
-      <c r="P9" s="9"/>
-    </row>
-    <row r="10" spans="1:16" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="15">
-        <v>4</v>
-      </c>
-      <c r="B10" s="26">
-        <v>135333</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16" t="s">
-        <v>141</v>
-      </c>
-      <c r="F10" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="J10" s="16"/>
-      <c r="K10" s="11">
-        <v>9856045470</v>
-      </c>
-      <c r="L10" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="M10" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="N10" s="13"/>
-      <c r="O10" s="13"/>
-      <c r="P10" s="9"/>
-    </row>
-    <row r="11" spans="1:16" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="15">
-        <v>5</v>
-      </c>
-      <c r="B11" s="26">
-        <v>103982</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="J11" s="16"/>
-      <c r="K11" s="11">
-        <v>985606347</v>
-      </c>
-      <c r="L11" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="M11" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="N11" s="13"/>
-      <c r="O11" s="13"/>
-      <c r="P11" s="9"/>
-    </row>
-    <row r="12" spans="1:16" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="15">
-        <v>6</v>
-      </c>
-      <c r="B12" s="26">
-        <v>190822</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16" t="s">
-        <v>142</v>
-      </c>
-      <c r="F12" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="J12" s="16"/>
-      <c r="K12" s="11">
-        <v>9846111816</v>
-      </c>
-      <c r="L12" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="M12" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="N12" s="13"/>
-      <c r="O12" s="13"/>
-      <c r="P12" s="9"/>
-    </row>
-    <row r="13" spans="1:16" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="15">
-        <v>7</v>
-      </c>
-      <c r="B13" s="26">
-        <v>203926</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="F13" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="J13" s="16"/>
-      <c r="K13" s="11">
-        <v>9857659107</v>
-      </c>
-      <c r="L13" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="M13" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="N13" s="13"/>
-      <c r="O13" s="13"/>
-      <c r="P13" s="9"/>
-    </row>
-    <row r="14" spans="1:16" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="15">
-        <v>8</v>
-      </c>
-      <c r="B14" s="26">
-        <v>150069</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="F14" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="J14" s="16"/>
-      <c r="K14" s="11">
-        <v>9856036830</v>
-      </c>
-      <c r="L14" s="13"/>
-      <c r="M14" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="N14" s="13"/>
-      <c r="O14" s="13"/>
-      <c r="P14" s="9"/>
-    </row>
-    <row r="15" spans="1:16" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="15">
-        <v>9</v>
-      </c>
-      <c r="B15" s="26">
-        <v>129444</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="F15" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="J15" s="16"/>
-      <c r="K15" s="11">
-        <v>9846062103</v>
-      </c>
-      <c r="L15" s="13"/>
-      <c r="M15" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="N15" s="13"/>
-      <c r="O15" s="13"/>
-      <c r="P15" s="9"/>
-    </row>
-    <row r="16" spans="1:16" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="15">
-        <v>10</v>
-      </c>
-      <c r="B16" s="26">
-        <v>227510</v>
-      </c>
-      <c r="C16" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="F16" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="J16" s="16"/>
-      <c r="K16" s="11">
-        <v>9846417379</v>
-      </c>
-      <c r="L16" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="M16" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="N16" s="13"/>
-      <c r="O16" s="13"/>
-      <c r="P16" s="9"/>
-    </row>
-    <row r="17" spans="1:16" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="15">
-        <v>11</v>
-      </c>
-      <c r="B17" s="26"/>
-      <c r="C17" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="13"/>
-      <c r="M17" s="13"/>
-      <c r="N17" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="O17" s="13"/>
-      <c r="P17" s="9"/>
-    </row>
-    <row r="18" spans="1:16" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="15">
-        <v>12</v>
-      </c>
-      <c r="B18" s="26"/>
-      <c r="C18" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="13"/>
-      <c r="N18" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="O18" s="13"/>
-      <c r="P18" s="9"/>
-    </row>
-    <row r="19" spans="1:16" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="15">
-        <v>13</v>
-      </c>
-      <c r="B19" s="26">
-        <v>167986</v>
-      </c>
-      <c r="C19" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="F19" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="J19" s="16"/>
-      <c r="K19" s="11">
-        <v>9856080588</v>
-      </c>
-      <c r="L19" s="13"/>
-      <c r="M19" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="N19" s="13"/>
-      <c r="O19" s="13"/>
-      <c r="P19" s="9"/>
-    </row>
-    <row r="20" spans="1:16" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="15">
-        <v>14</v>
-      </c>
-      <c r="B20" s="26">
-        <v>140508</v>
-      </c>
-      <c r="C20" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16" t="s">
-        <v>147</v>
-      </c>
-      <c r="F20" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="J20" s="16"/>
-      <c r="K20" s="11">
-        <v>9846060963</v>
-      </c>
-      <c r="L20" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="M20" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="N20" s="13"/>
-      <c r="O20" s="13"/>
-      <c r="P20" s="9"/>
-    </row>
-    <row r="21" spans="1:16" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="15">
-        <v>15</v>
-      </c>
-      <c r="B21" s="26">
-        <v>166978</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16" t="s">
-        <v>147</v>
-      </c>
-      <c r="F21" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="J21" s="16"/>
-      <c r="K21" s="11">
-        <v>9846030628</v>
-      </c>
-      <c r="L21" s="13"/>
-      <c r="M21" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="N21" s="13"/>
-      <c r="O21" s="13"/>
-      <c r="P21" s="9"/>
-    </row>
-    <row r="22" spans="1:16" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A22" s="15">
-        <v>16</v>
-      </c>
-      <c r="B22" s="26">
-        <v>182980</v>
-      </c>
-      <c r="C22" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16" t="s">
-        <v>147</v>
-      </c>
-      <c r="F22" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="J22" s="16"/>
-      <c r="K22" s="11">
-        <v>9845416400</v>
-      </c>
-      <c r="L22" s="12"/>
-      <c r="M22" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="N22" s="12"/>
-      <c r="O22" s="12"/>
-      <c r="P22" s="9"/>
-    </row>
-    <row r="23" spans="1:16" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A23" s="15">
-        <v>17</v>
-      </c>
-      <c r="B23" s="26">
-        <v>170653</v>
-      </c>
-      <c r="C23" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16" t="s">
-        <v>147</v>
-      </c>
-      <c r="F23" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="J23" s="16"/>
-      <c r="K23" s="11">
-        <v>9846329585</v>
-      </c>
-      <c r="L23" s="12"/>
-      <c r="M23" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="N23" s="12"/>
-      <c r="O23" s="12"/>
-      <c r="P23" s="9"/>
-    </row>
-    <row r="24" spans="1:16" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A24" s="15">
-        <v>18</v>
-      </c>
-      <c r="B24" s="26">
-        <v>150701</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16" t="s">
-        <v>147</v>
-      </c>
-      <c r="F24" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="J24" s="16"/>
-      <c r="K24" s="11">
-        <v>9846055789</v>
-      </c>
-      <c r="L24" s="12"/>
-      <c r="M24" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="N24" s="12"/>
-      <c r="O24" s="12"/>
-      <c r="P24" s="9"/>
-    </row>
-    <row r="25" spans="1:16" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A25" s="15">
-        <v>19</v>
-      </c>
-      <c r="B25" s="38" t="s">
-        <v>132</v>
-      </c>
-      <c r="C25" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
-      <c r="J25" s="16"/>
-      <c r="K25" s="11"/>
-      <c r="L25" s="6"/>
-      <c r="M25" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="N25" s="6"/>
-      <c r="O25" s="6"/>
-      <c r="P25" s="9"/>
-    </row>
-    <row r="26" spans="1:16" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A26" s="15">
-        <v>20</v>
-      </c>
-      <c r="B26" s="26">
-        <v>135482</v>
-      </c>
-      <c r="C26" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="F26" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="J26" s="16"/>
-      <c r="K26" s="11">
-        <v>9846233996</v>
-      </c>
-      <c r="L26" s="6"/>
-      <c r="M26" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="N26" s="6"/>
-      <c r="O26" s="6"/>
-      <c r="P26" s="9"/>
-    </row>
-    <row r="27" spans="1:16" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A27" s="15">
-        <v>21</v>
-      </c>
-      <c r="B27" s="26">
-        <v>130492</v>
-      </c>
-      <c r="C27" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="F27" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="G27" s="16"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="J27" s="16"/>
-      <c r="K27" s="11">
-        <v>9846090694</v>
-      </c>
-      <c r="L27" s="6"/>
-      <c r="M27" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="N27" s="6"/>
-      <c r="O27" s="6"/>
-      <c r="P27" s="9"/>
-    </row>
-  </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="M6:O6"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A2:P2"/>
-    <mergeCell ref="A3:P3"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="P6:P7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H6:J6"/>
-  </mergeCells>
-  <phoneticPr fontId="9" type="noConversion"/>
-  <pageMargins left="0.71" right="0.26" top="0.34" bottom="0.26" header="0.3" footer="0.3"/>
-  <pageSetup scale="62" orientation="landscape" r:id="rId1"/>
-</worksheet>
 </file>